--- a/supplementary_data_1_full_performance_metrics_bootstrap_paired_contrasts.xlsx
+++ b/supplementary_data_1_full_performance_metrics_bootstrap_paired_contrasts.xlsx
@@ -33,20 +33,15 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,13 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,14 +432,14 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -673,7 +676,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.981</v>
+        <v>0.952</v>
       </c>
       <c r="D8" t="n">
         <v>0.622</v>
@@ -682,13 +685,13 @@
         <v>0.481</v>
       </c>
       <c r="F8" t="n">
-        <v>0.989</v>
+        <v>0.972</v>
       </c>
       <c r="G8" t="n">
-        <v>0.646</v>
+        <v>0.639</v>
       </c>
       <c r="H8" t="n">
-        <v>0.532</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +706,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.971</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0.696</v>
@@ -712,13 +715,13 @@
         <v>0.533</v>
       </c>
       <c r="F9" t="n">
-        <v>0.985</v>
+        <v>0.971</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="H9" t="n">
-        <v>0.588</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +736,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.999</v>
+        <v>0.97</v>
       </c>
       <c r="D10" t="n">
         <v>0.724</v>
@@ -742,13 +745,13 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="G10" t="n">
-        <v>0.721</v>
+        <v>0.713</v>
       </c>
       <c r="H10" t="n">
-        <v>0.638</v>
+        <v>0.617</v>
       </c>
     </row>
   </sheetData>
@@ -765,7 +768,7 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -1082,32 +1085,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.981 (0.976--0.985)</t>
+          <t>0.952 (0.945--0.958)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.622 (0.613--0.632)</t>
+          <t>0.622 (0.613--0.631)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.481 (0.471--0.492)</t>
+          <t>0.481 (0.470--0.492)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.989 (0.987--0.991)</t>
+          <t>0.972 (0.968--0.976)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.646 (0.636--0.656)</t>
+          <t>0.639 (0.629--0.649)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.532 (0.523--0.542)</t>
+          <t>0.510 (0.500--0.521)</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1127,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.971 (0.966--0.976)</t>
+          <t>0.943 (0.936--0.950)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1134,22 +1137,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.533 (0.521--0.545)</t>
+          <t>0.533 (0.521--0.544)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.985 (0.983--0.988)</t>
+          <t>0.971 (0.967--0.974)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.688 (0.678--0.699)</t>
+          <t>0.681 (0.671--0.691)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.588 (0.578--0.599)</t>
+          <t>0.567 (0.556--0.578)</t>
         </is>
       </c>
     </row>
@@ -1166,32 +1169,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.999 (0.998--1.000)</t>
+          <t>0.970 (0.964--0.975)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.724 (0.715--0.733)</t>
+          <t>0.724 (0.715--0.732)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.564 (0.552--0.576)</t>
+          <t>0.564 (0.552--0.575)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.000 (0.999--1.000)</t>
+          <t>0.985 (0.982--0.987)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.721 (0.711--0.731)</t>
+          <t>0.713 (0.703--0.722)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.638 (0.629--0.648)</t>
+          <t>0.617 (0.607--0.627)</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1212,7 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1259,14 +1262,12 @@
           <t>Sensitivity</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+0.028</t>
-        </is>
+      <c r="D2" t="n">
+        <v>0.027</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+0.023 to +0.033</t>
+          <t>+0.022 to +0.032</t>
         </is>
       </c>
     </row>
@@ -1286,10 +1287,8 @@
           <t>Specificity</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+0.028</t>
-        </is>
+      <c r="D3" t="n">
+        <v>0.028</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1313,10 +1312,8 @@
           <t>PPV</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+0.031</t>
-        </is>
+      <c r="D4" t="n">
+        <v>0.031</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1340,10 +1337,8 @@
           <t>NPV</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+0.014</t>
-        </is>
+      <c r="D5" t="n">
+        <v>0.014</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1367,14 +1362,12 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.033</t>
-        </is>
+      <c r="D6" t="n">
+        <v>0.032</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+0.028 to +0.037</t>
+          <t>+0.027 to +0.037</t>
         </is>
       </c>
     </row>
@@ -1394,10 +1387,8 @@
           <t>MCC</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+0.050</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0.05</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1421,14 +1412,12 @@
           <t>Sensitivity</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+0.018</t>
-        </is>
+      <c r="D8" t="n">
+        <v>0.018</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+0.014 to +0.023</t>
+          <t>+0.014 to +0.022</t>
         </is>
       </c>
     </row>
@@ -1448,10 +1437,8 @@
           <t>Specificity</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+0.102</t>
-        </is>
+      <c r="D9" t="n">
+        <v>0.102</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1475,10 +1462,8 @@
           <t>PPV</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>+0.083</t>
-        </is>
+      <c r="D10" t="n">
+        <v>0.083</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1502,14 +1487,12 @@
           <t>NPV</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>+0.011</t>
-        </is>
+      <c r="D11" t="n">
+        <v>0.013</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+0.008 to +0.013</t>
+          <t>+0.010 to +0.015</t>
         </is>
       </c>
     </row>
@@ -1529,14 +1512,12 @@
           <t>F1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>+0.075</t>
-        </is>
+      <c r="D12" t="n">
+        <v>0.074</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+0.071 to +0.080</t>
+          <t>+0.070 to +0.078</t>
         </is>
       </c>
     </row>
@@ -1556,14 +1537,12 @@
           <t>MCC</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>+0.106</t>
-        </is>
+      <c r="D13" t="n">
+        <v>0.107</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+0.100 to +0.112</t>
+          <t>+0.100 to +0.113</t>
         </is>
       </c>
     </row>
@@ -1581,21 +1560,21 @@
   <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1716,7 +1695,6 @@
       <c r="L2" t="n">
         <v>0.928</v>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0.821</v>
       </c>
@@ -1765,7 +1743,6 @@
       <c r="L3" t="n">
         <v>0.86</v>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>0.755</v>
       </c>
@@ -1814,7 +1791,6 @@
       <c r="L4" t="n">
         <v>0.845</v>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>0.715</v>
       </c>
@@ -1863,7 +1839,6 @@
       <c r="L5" t="n">
         <v>0.771</v>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>0.648</v>
       </c>
@@ -1883,7 +1858,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1900,10 +1875,10 @@
         <v>5556</v>
       </c>
       <c r="H6" t="n">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="I6" t="n">
-        <v>0.979</v>
+        <v>0.951</v>
       </c>
       <c r="J6" t="n">
         <v>0.497</v>
@@ -1912,16 +1887,16 @@
         <v>0.41</v>
       </c>
       <c r="L6" t="n">
-        <v>0.985</v>
+        <v>0.965</v>
       </c>
       <c r="M6" t="n">
-        <v>0.624</v>
+        <v>0.619</v>
       </c>
       <c r="N6" t="n">
-        <v>0.578</v>
+        <v>0.573</v>
       </c>
       <c r="O6" t="n">
-        <v>0.434</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="7">
@@ -1936,7 +1911,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1944,7 +1919,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3653</v>
+        <v>3727</v>
       </c>
       <c r="F7" t="n">
         <v>4366</v>
@@ -1953,28 +1928,28 @@
         <v>6676</v>
       </c>
       <c r="H7" t="n">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="I7" t="n">
-        <v>0.926</v>
+        <v>0.916</v>
       </c>
       <c r="J7" t="n">
         <v>0.395</v>
       </c>
       <c r="K7" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="M7" t="n">
-        <v>0.535</v>
+        <v>0.536</v>
       </c>
       <c r="N7" t="n">
-        <v>0.512</v>
+        <v>0.515</v>
       </c>
       <c r="O7" t="n">
-        <v>0.305</v>
+        <v>0.299</v>
       </c>
     </row>
   </sheetData>
@@ -1991,24 +1966,24 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2115,10 +2090,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D2" t="n">
-        <v>3947</v>
+        <v>4067</v>
       </c>
       <c r="E2" t="n">
         <v>11042</v>
@@ -2127,7 +2102,7 @@
         <v>9422</v>
       </c>
       <c r="G2" t="n">
-        <v>5567</v>
+        <v>5687</v>
       </c>
       <c r="H2" t="n">
         <v>3866</v>
@@ -2139,10 +2114,10 @@
         <v>5556</v>
       </c>
       <c r="K2" t="n">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="L2" t="n">
-        <v>0.979</v>
+        <v>0.951</v>
       </c>
       <c r="M2" t="n">
         <v>0.497</v>
@@ -2151,16 +2126,16 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>0.985</v>
+        <v>0.965</v>
       </c>
       <c r="P2" t="n">
-        <v>0.624</v>
+        <v>0.619</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.578</v>
+        <v>0.573</v>
       </c>
       <c r="R2" t="n">
-        <v>0.434</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="3">
@@ -2175,22 +2150,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D3" t="n">
-        <v>3947</v>
+        <v>4067</v>
       </c>
       <c r="E3" t="n">
         <v>11042</v>
       </c>
       <c r="F3" t="n">
-        <v>10329</v>
+        <v>10403</v>
       </c>
       <c r="G3" t="n">
-        <v>4660</v>
+        <v>4706</v>
       </c>
       <c r="H3" t="n">
-        <v>3653</v>
+        <v>3727</v>
       </c>
       <c r="I3" t="n">
         <v>4366</v>
@@ -2199,28 +2174,28 @@
         <v>6676</v>
       </c>
       <c r="K3" t="n">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.926</v>
+        <v>0.916</v>
       </c>
       <c r="M3" t="n">
         <v>0.395</v>
       </c>
       <c r="N3" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="P3" t="n">
-        <v>0.535</v>
+        <v>0.536</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.512</v>
+        <v>0.515</v>
       </c>
       <c r="R3" t="n">
-        <v>0.305</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="4">
@@ -2235,10 +2210,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D4" t="n">
-        <v>3947</v>
+        <v>4067</v>
       </c>
       <c r="E4" t="n">
         <v>11042</v>
@@ -2247,7 +2222,7 @@
         <v>8046</v>
       </c>
       <c r="G4" t="n">
-        <v>6943</v>
+        <v>7063</v>
       </c>
       <c r="H4" t="n">
         <v>3871</v>
@@ -2259,10 +2234,10 @@
         <v>4175</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="L4" t="n">
-        <v>0.981</v>
+        <v>0.952</v>
       </c>
       <c r="M4" t="n">
         <v>0.622</v>
@@ -2271,16 +2246,16 @@
         <v>0.481</v>
       </c>
       <c r="O4" t="n">
-        <v>0.989</v>
+        <v>0.972</v>
       </c>
       <c r="P4" t="n">
-        <v>0.716</v>
+        <v>0.711</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.646</v>
+        <v>0.639</v>
       </c>
       <c r="R4" t="n">
-        <v>0.532</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="5">
@@ -2295,22 +2270,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D5" t="n">
-        <v>3947</v>
+        <v>4067</v>
       </c>
       <c r="E5" t="n">
         <v>11042</v>
       </c>
       <c r="F5" t="n">
-        <v>7196</v>
+        <v>7197</v>
       </c>
       <c r="G5" t="n">
-        <v>7793</v>
+        <v>7912</v>
       </c>
       <c r="H5" t="n">
-        <v>3834</v>
+        <v>3835</v>
       </c>
       <c r="I5" t="n">
         <v>7680</v>
@@ -2319,10 +2294,10 @@
         <v>3362</v>
       </c>
       <c r="K5" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="L5" t="n">
-        <v>0.971</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>0.696</v>
@@ -2331,16 +2306,16 @@
         <v>0.533</v>
       </c>
       <c r="O5" t="n">
-        <v>0.985</v>
+        <v>0.971</v>
       </c>
       <c r="P5" t="n">
-        <v>0.768</v>
+        <v>0.762</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="R5" t="n">
-        <v>0.588</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2355,10 +2330,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14989</v>
+        <v>15109</v>
       </c>
       <c r="D6" t="n">
-        <v>3947</v>
+        <v>4067</v>
       </c>
       <c r="E6" t="n">
         <v>11042</v>
@@ -2367,7 +2342,7 @@
         <v>6996</v>
       </c>
       <c r="G6" t="n">
-        <v>7993</v>
+        <v>8113</v>
       </c>
       <c r="H6" t="n">
         <v>3944</v>
@@ -2379,10 +2354,10 @@
         <v>3052</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="L6" t="n">
-        <v>0.999</v>
+        <v>0.97</v>
       </c>
       <c r="M6" t="n">
         <v>0.724</v>
@@ -2391,16 +2366,16 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="P6" t="n">
-        <v>0.796</v>
+        <v>0.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.721</v>
+        <v>0.713</v>
       </c>
       <c r="R6" t="n">
-        <v>0.638</v>
+        <v>0.617</v>
       </c>
     </row>
   </sheetData>

--- a/supplementary_data_1_full_performance_metrics_bootstrap_paired_contrasts.xlsx
+++ b/supplementary_data_1_full_performance_metrics_bootstrap_paired_contrasts.xlsx
@@ -2004,12 +2004,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>AAS-positive</t>
+          <t>AD-positive</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>AAS-negative</t>
+          <t>AD-negative</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
